--- a/deliverables/exports/track-b/07-customer-journey.xlsx
+++ b/deliverables/exports/track-b/07-customer-journey.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -660,75 +660,110 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Acceleration opportunities</t>
+          <t>Added from Block 1 research, why buyers actually go quiet</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>• Compress stage 2 to stage 5 for the founding cohort. Eight to twelve people</t>
+          <t>The original version of stage 1 treated the unexplained loss as something the member never gets a reason for. `00-BUYER-CHECKS.md` supplies the mechanism and it is a better story than the one this funnel was built on.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>recruited directly skip stages 1 through 4 entirely. That is the fastest route to a room that is not empty, and Phase 5 Step 5.2 is the mechanism.</t>
+          <t>**The champion could not sell the vendor internally.** A North American buyer runs four parallel lanes, procurement, legal and privacy, IT and security, and finance, and go-live is gated on all four clearing. Deals stall when the buyer-side advocate has nothing to hand each lane. The good first call was real. What followed was an advocate carrying no documents into three departments that never met the vendor.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>• Make stage 5's first action a booking, not a browse. A teardown slot booked in</t>
+          <t>Separately, a 90 to 180 day enterprise cycle with no contact looks identical to rejection from outside. Some of what members read as ghosting is a normal cycle.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>week one converts a passive member into someone with a deadline. This is the single highest impact change available against the 14 day churn number.</t>
+          <t>**What this changes in this funnel.** Stage 1's trigger stays the same, an unexplained loss. What the member is taught to do about it changes from presenting better to arming the champion. That is a different asset set and a more teachable one, and it should be reflected here once `00-CONFLICTS-TO-RESOLVE.md` conflict 2 settles who this track is for.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>• Publish the checklist for free and in full. It costs one asset and it does</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration opportunities</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>stage 1 and stage 2 work at the same time. The offer is not the checklist, it is the application of it to the member's own deal, which cannot be given away.</t>
+          <t>• Compress stage 2 to stage 5 for the founding cohort. Eight to twelve people</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>• Solve stage 4 payment as a growth project, not an operations task. Annual</t>
+          <t>recruited directly skip stages 1 through 4 entirely. That is the fastest route to a room that is not empty, and Phase 5 Step 5.2 is the mechanism.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>billing, cohort billing, and a local collection route each recover members who already decided to buy. That is the cheapest conversion available anywhere in this funnel.</t>
+          <t>• Make stage 5's first action a booking, not a browse. A teardown slot booked in</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>week one converts a passive member into someone with a deadline. This is the single highest impact change available against the 14 day churn number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>• Publish the checklist for free and in full. It costs one asset and it does</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>stage 1 and stage 2 work at the same time. The offer is not the checklist, it is the application of it to the member's own deal, which cannot be given away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>• Solve stage 4 payment as a growth project, not an operations task. Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>billing, cohort billing, and a local collection route each recover members who already decided to buy. That is the cheapest conversion available anywhere in this funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
         </is>

--- a/deliverables/exports/track-b/07-customer-journey.xlsx
+++ b/deliverables/exports/track-b/07-customer-journey.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -688,82 +688,89 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>**What this changes in this funnel.** Stage 1's trigger stays the same, an unexplained loss. What the member is taught to do about it changes from presenting better to arming the champion. That is a different asset set and a more teachable one, and it should be reflected here once `00-CONFLICTS-TO-RESOLVE.md` conflict 2 settles who this track is for.</t>
+          <t>**What this changes in this funnel.** Stage 1's trigger stays the same, an unexplained loss. What the member is taught to do about it changes from presenting better to arming the champion. Champion enablement is now dimension 6 of the scorecard, and it is the dimension most respondents will score lowest on while being free to fix, which makes it the best single piece of content in the top of funnel.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>**And a blocker this funnel now avoids.** Conflict 2 resolved as the ladder, see `00-RESOLUTIONS.md`. Stage 5's churn risk was always that a member arrives and finds nothing relevant. Teaching enterprise procurement to a band 1 member would have guaranteed it. The bands mean a member at any position has a next rung, and the first rungs cost nothing but knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Acceleration opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>• Compress stage 2 to stage 5 for the founding cohort. Eight to twelve people</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>recruited directly skip stages 1 through 4 entirely. That is the fastest route to a room that is not empty, and Phase 5 Step 5.2 is the mechanism.</t>
+          <t>• Compress stage 2 to stage 5 for the founding cohort. Eight to twelve people</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>• Make stage 5's first action a booking, not a browse. A teardown slot booked in</t>
+          <t>recruited directly skip stages 1 through 4 entirely. That is the fastest route to a room that is not empty, and Phase 5 Step 5.2 is the mechanism.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>week one converts a passive member into someone with a deadline. This is the single highest impact change available against the 14 day churn number.</t>
+          <t>• Make stage 5's first action a booking, not a browse. A teardown slot booked in</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>• Publish the checklist for free and in full. It costs one asset and it does</t>
+          <t>week one converts a passive member into someone with a deadline. This is the single highest impact change available against the 14 day churn number.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>stage 1 and stage 2 work at the same time. The offer is not the checklist, it is the application of it to the member's own deal, which cannot be given away.</t>
+          <t>• Publish the checklist for free and in full. It costs one asset and it does</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>• Solve stage 4 payment as a growth project, not an operations task. Annual</t>
+          <t>stage 1 and stage 2 work at the same time. The offer is not the checklist, it is the application of it to the member's own deal, which cannot be given away.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>billing, cohort billing, and a local collection route each recover members who already decided to buy. That is the cheapest conversion available anywhere in this funnel.</t>
+          <t>• Solve stage 4 payment as a growth project, not an operations task. Annual</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>billing, cohort billing, and a local collection route each recover members who already decided to buy. That is the cheapest conversion available anywhere in this funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
         </is>
@@ -896,12 +903,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Scorecard starts. Completion rate, the real number. Email capture</t>
+          <t>Scorecard starts. Completion rate, the real number. Email capture. Band distribution, which says whether the audience being reached is servable</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Has a per dimension score and a named weakest dimension, in their own words</t>
+          <t>Has a per dimension score, a named weakest dimension, and a band position</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
